--- a/docs/vystupy/nakladova-struktura.xlsx
+++ b/docs/vystupy/nakladova-struktura.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$Kč-405]_-;\-* #,##0.00\ [$Kč-405]_-;_-* &quot;-&quot;??\ [$Kč-405]_-;_-@_-"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Aptos Narrow"/>
       <charset val="238"/>
@@ -36,6 +36,9 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,12 +61,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,150 +466,277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33.140625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="13.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Tarif</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Cena_Mesic_CZK</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Kapacita_Psu</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Podil_Treneru</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Vynos_CZK</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Parametr</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Hodnota</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Jednotka</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Solo trenér</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>490</v>
+          <t>Cena_za_aktivniho_klienta</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Kč / měsíc</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>do 15 psů</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F2">
-        <f>C2*E2</f>
-        <v/>
+          <t>Trenér platí za každého aktivního klienta nad limit zdarma</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Psí škola / Pro</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>990</v>
+          <t>Klienti_zdarma</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>klienti / trenér</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>neomezeně</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F3">
-        <f>C3*E3</f>
-        <v/>
+          <t>Vyzkoušení bez platby</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Psovod (klient)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+          <t>Strop_na_trenera</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1490</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kč / měsíc</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>více psů (pod trenérem)</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <f>C4*E4</f>
-        <v/>
+          <t>Psí školy, strop platí od 34 aktivních klientů</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Cena_pro_psovoda</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kč</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S trenérem i bez něj, i s více psy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prumer_klientu_na_trenera</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>klienti</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Předpoklad pro pilot (respondentka má ~40 klientů)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Prirazka_trenera_klientovi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kč / měsíc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Návrh: kolik si trenér řekne klientovi za podporu mezi lekcemi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Aktivních klientů</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Poplatek trenéra</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Příjem trenéra z přirážky</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Trenérovi zbyde</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2">
+        <f>MIN($B$4,MAX(0,A10-$B$3)*$B$2)</f>
+        <v/>
+      </c>
+      <c r="C10" s="2">
+        <f>A10*$B$7</f>
+        <v/>
+      </c>
+      <c r="D10" s="2">
+        <f>C10-B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <f>MIN($B$4,MAX(0,A11-$B$3)*$B$2)</f>
+        <v/>
+      </c>
+      <c r="C11" s="2">
+        <f>A11*$B$7</f>
+        <v/>
+      </c>
+      <c r="D11" s="2">
+        <f>C11-B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <f>MIN($B$4,MAX(0,A12-$B$3)*$B$2)</f>
+        <v/>
+      </c>
+      <c r="C12" s="2">
+        <f>A12*$B$7</f>
+        <v/>
+      </c>
+      <c r="D12" s="2">
+        <f>C12-B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>40</v>
+      </c>
+      <c r="B13" s="2">
+        <f>MIN($B$4,MAX(0,A13-$B$3)*$B$2)</f>
+        <v/>
+      </c>
+      <c r="C13" s="2">
+        <f>A13*$B$7</f>
+        <v/>
+      </c>
+      <c r="D13" s="2">
+        <f>C13-B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>ARPU</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Průměrný měsíční příjem na trenéra</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <f>SUM(F2:F4)</f>
-        <v/>
+      <c r="B15" s="6">
+        <f>MIN(B4,MAX(0,B6-B3)*B2)</f>
+        <v/>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kč / měsíc</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Průměrný měsíční příjem na platícího trenéra (při B6 klientech)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Aktivní klient = psovod propojený s trenérem, se kterým trenér v měsíci aspoň jednou pracoval v aplikaci (zadání, úprava plánu, záznam nebo zpráva).</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -778,73 +910,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="26" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
-    <col width="12" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
-    <col width="12.7109375" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
-    <col width="14.7109375" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="13.140625" bestFit="1" customWidth="1" style="2" min="10" max="10"/>
-    <col width="21" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Mesic</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Platici_Treneri</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Aktivni_Psi</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Aktivni_Klienti</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Psovodi_Bez_Trenera</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Prijmy_Celkem</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Server_DB</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Frontend_API</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Notifikace</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Poplatky_Brany</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>OPEX_Celkem</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Mesicni_Zisk</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Kumulativni_Cashflow</t>
         </is>
@@ -859,15 +998,16 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2">
-        <f>B2*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
+      <c r="C2">
+        <f>B2*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2">
+        <f>MIN(B2*Unit_Economics!$B$4,MAX(0,C2-B2*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -875,20 +1015,23 @@
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2">
-        <f>D2*0.02</f>
-        <v/>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <f>SUM(E2:H2)</f>
+        <f>E2*0.02</f>
         <v/>
       </c>
       <c r="J2" s="2">
-        <f>D2-I2</f>
+        <f>SUM(F2:I2)</f>
         <v/>
       </c>
       <c r="K2" s="2">
-        <f>-CAPEX!$D$6+J2</f>
+        <f>E2-J2</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>-CAPEX!$D$6+K2</f>
         <v/>
       </c>
     </row>
@@ -901,15 +1044,16 @@
       <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D3" s="2">
-        <f>B3*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
+      <c r="C3">
+        <f>B3*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2">
+        <f>MIN(B3*Unit_Economics!$B$4,MAX(0,C3-B3*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -917,20 +1061,23 @@
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="2">
-        <f>D3*0.02</f>
-        <v/>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <f>SUM(E3:H3)</f>
+        <f>E3*0.02</f>
         <v/>
       </c>
       <c r="J3" s="2">
-        <f>D3-I3</f>
+        <f>SUM(F3:I3)</f>
         <v/>
       </c>
       <c r="K3" s="2">
-        <f>K2+J3</f>
+        <f>E3-J3</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>L2+K3</f>
         <v/>
       </c>
     </row>
@@ -943,15 +1090,16 @@
       <c r="B4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D4" s="2">
-        <f>B4*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
+      <c r="C4">
+        <f>B4*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2">
+        <f>MIN(B4*Unit_Economics!$B$4,MAX(0,C4-B4*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -959,20 +1107,23 @@
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="2">
-        <f>D4*0.02</f>
-        <v/>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <f>SUM(E4:H4)</f>
+        <f>E4*0.02</f>
         <v/>
       </c>
       <c r="J4" s="2">
-        <f>D4-I4</f>
+        <f>SUM(F4:I4)</f>
         <v/>
       </c>
       <c r="K4" s="2">
-        <f>K3+J4</f>
+        <f>E4-J4</f>
+        <v/>
+      </c>
+      <c r="L4" s="2">
+        <f>L3+K4</f>
         <v/>
       </c>
     </row>
@@ -985,36 +1136,40 @@
       <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" t="n">
-        <v>45</v>
-      </c>
-      <c r="D5" s="2">
-        <f>B5*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="C5">
+        <f>B5*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="2">
+        <f>MIN(B5*Unit_Economics!$B$4,MAX(0,C5-B5*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
-        <f>D5*0.02</f>
-        <v/>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <f>SUM(E5:H5)</f>
+        <f>E5*0.02</f>
         <v/>
       </c>
       <c r="J5" s="2">
-        <f>D5-I5</f>
+        <f>SUM(F5:I5)</f>
         <v/>
       </c>
       <c r="K5" s="2">
-        <f>K4+J5</f>
+        <f>E5-J5</f>
+        <v/>
+      </c>
+      <c r="L5" s="2">
+        <f>L4+K5</f>
         <v/>
       </c>
     </row>
@@ -1027,36 +1182,40 @@
       <c r="B6" t="n">
         <v>6</v>
       </c>
-      <c r="C6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D6" s="2">
-        <f>B6*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="C6">
+        <f>B6*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="2">
+        <f>MIN(B6*Unit_Economics!$B$4,MAX(0,C6-B6*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="2">
-        <f>D6*0.02</f>
-        <v/>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <f>SUM(E6:H6)</f>
+        <f>E6*0.02</f>
         <v/>
       </c>
       <c r="J6" s="2">
-        <f>D6-I6</f>
+        <f>SUM(F6:I6)</f>
         <v/>
       </c>
       <c r="K6" s="2">
-        <f>K5+J6</f>
+        <f>E6-J6</f>
+        <v/>
+      </c>
+      <c r="L6" s="2">
+        <f>L5+K6</f>
         <v/>
       </c>
     </row>
@@ -1069,36 +1228,40 @@
       <c r="B7" t="n">
         <v>10</v>
       </c>
-      <c r="C7" t="n">
-        <v>110</v>
-      </c>
-      <c r="D7" s="2">
-        <f>B7*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E7" s="2" t="n">
+      <c r="C7">
+        <f>B7*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="2">
+        <f>MIN(B7*Unit_Economics!$B$4,MAX(0,C7-B7*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="2">
-        <f>D7*0.02</f>
-        <v/>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <f>SUM(E7:H7)</f>
+        <f>E7*0.02</f>
         <v/>
       </c>
       <c r="J7" s="2">
-        <f>D7-I7</f>
+        <f>SUM(F7:I7)</f>
         <v/>
       </c>
       <c r="K7" s="2">
-        <f>K6+J7</f>
+        <f>E7-J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="2">
+        <f>L6+K7</f>
         <v/>
       </c>
     </row>
@@ -1111,36 +1274,40 @@
       <c r="B8" t="n">
         <v>13</v>
       </c>
-      <c r="C8" t="n">
-        <v>140</v>
-      </c>
-      <c r="D8" s="2">
-        <f>B8*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E8" s="2" t="n">
+      <c r="C8">
+        <f>B8*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E8" s="2">
+        <f>MIN(B8*Unit_Economics!$B$4,MAX(0,C8-B8*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="2">
-        <f>D8*0.02</f>
-        <v/>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <f>SUM(E8:H8)</f>
+        <f>E8*0.02</f>
         <v/>
       </c>
       <c r="J8" s="2">
-        <f>D8-I8</f>
+        <f>SUM(F8:I8)</f>
         <v/>
       </c>
       <c r="K8" s="2">
-        <f>K7+J8</f>
+        <f>E8-J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="2">
+        <f>L7+K8</f>
         <v/>
       </c>
     </row>
@@ -1153,36 +1320,40 @@
       <c r="B9" t="n">
         <v>16</v>
       </c>
-      <c r="C9" t="n">
-        <v>180</v>
-      </c>
-      <c r="D9" s="2">
-        <f>B9*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E9" s="2" t="n">
+      <c r="C9">
+        <f>B9*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D9" t="n">
+        <v>80</v>
+      </c>
+      <c r="E9" s="2">
+        <f>MIN(B9*Unit_Economics!$B$4,MAX(0,C9-B9*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H9" s="2">
-        <f>D9*0.02</f>
-        <v/>
-      </c>
       <c r="I9" s="2">
-        <f>SUM(E9:H9)</f>
+        <f>E9*0.02</f>
         <v/>
       </c>
       <c r="J9" s="2">
-        <f>D9-I9</f>
+        <f>SUM(F9:I9)</f>
         <v/>
       </c>
       <c r="K9" s="2">
-        <f>K8+J9</f>
+        <f>E9-J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="2">
+        <f>L8+K9</f>
         <v/>
       </c>
     </row>
@@ -1195,36 +1366,40 @@
       <c r="B10" t="n">
         <v>20</v>
       </c>
-      <c r="C10" t="n">
-        <v>230</v>
-      </c>
-      <c r="D10" s="2">
-        <f>B10*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E10" s="2" t="n">
+      <c r="C10">
+        <f>B10*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E10" s="2">
+        <f>MIN(B10*Unit_Economics!$B$4,MAX(0,C10-B10*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H10" s="2">
-        <f>D10*0.02</f>
-        <v/>
-      </c>
       <c r="I10" s="2">
-        <f>SUM(E10:H10)</f>
+        <f>E10*0.02</f>
         <v/>
       </c>
       <c r="J10" s="2">
-        <f>D10-I10</f>
+        <f>SUM(F10:I10)</f>
         <v/>
       </c>
       <c r="K10" s="2">
-        <f>K9+J10</f>
+        <f>E10-J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>L9+K10</f>
         <v/>
       </c>
     </row>
@@ -1237,36 +1412,40 @@
       <c r="B11" t="n">
         <v>23</v>
       </c>
-      <c r="C11" t="n">
-        <v>270</v>
-      </c>
-      <c r="D11" s="2">
-        <f>B11*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E11" s="2" t="n">
+      <c r="C11">
+        <f>B11*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="2">
+        <f>MIN(B11*Unit_Economics!$B$4,MAX(0,C11-B11*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H11" s="2">
-        <f>D11*0.02</f>
-        <v/>
-      </c>
       <c r="I11" s="2">
-        <f>SUM(E11:H11)</f>
+        <f>E11*0.02</f>
         <v/>
       </c>
       <c r="J11" s="2">
-        <f>D11-I11</f>
+        <f>SUM(F11:I11)</f>
         <v/>
       </c>
       <c r="K11" s="2">
-        <f>K10+J11</f>
+        <f>E11-J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="2">
+        <f>L10+K11</f>
         <v/>
       </c>
     </row>
@@ -1279,36 +1458,40 @@
       <c r="B12" t="n">
         <v>26</v>
       </c>
-      <c r="C12" t="n">
-        <v>320</v>
-      </c>
-      <c r="D12" s="2">
-        <f>B12*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E12" s="2" t="n">
+      <c r="C12">
+        <f>B12*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D12" t="n">
+        <v>110</v>
+      </c>
+      <c r="E12" s="2">
+        <f>MIN(B12*Unit_Economics!$B$4,MAX(0,C12-B12*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H12" s="2">
-        <f>D12*0.02</f>
-        <v/>
-      </c>
       <c r="I12" s="2">
-        <f>SUM(E12:H12)</f>
+        <f>E12*0.02</f>
         <v/>
       </c>
       <c r="J12" s="2">
-        <f>D12-I12</f>
+        <f>SUM(F12:I12)</f>
         <v/>
       </c>
       <c r="K12" s="2">
-        <f>K11+J12</f>
+        <f>E12-J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="2">
+        <f>L11+K12</f>
         <v/>
       </c>
     </row>
@@ -1321,40 +1504,51 @@
       <c r="B13" t="n">
         <v>30</v>
       </c>
-      <c r="C13" t="n">
-        <v>380</v>
-      </c>
-      <c r="D13" s="2">
-        <f>B13*Unit_Economics!$F$5</f>
-        <v/>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="C13">
+        <f>B13*Unit_Economics!$B$6</f>
+        <v/>
+      </c>
+      <c r="D13" t="n">
+        <v>120</v>
+      </c>
+      <c r="E13" s="2">
+        <f>MIN(B13*Unit_Economics!$B$4,MAX(0,C13-B13*Unit_Economics!$B$3)*Unit_Economics!$B$2)</f>
+        <v/>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="H13" s="2">
-        <f>D13*0.02</f>
-        <v/>
-      </c>
       <c r="I13" s="2">
-        <f>SUM(E13:H13)</f>
+        <f>E13*0.02</f>
         <v/>
       </c>
       <c r="J13" s="2">
-        <f>D13-I13</f>
+        <f>SUM(F13:I13)</f>
         <v/>
       </c>
       <c r="K13" s="2">
-        <f>K12+J13</f>
-        <v/>
+        <f>E13-J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="2">
+        <f>L12+K13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Příjmy = (aktivní klienti − 3 zdarma × platící trenéři) × 49 Kč, nejvýš strop 1 490 Kč na trenéra. Psovodi bez trenéra jsou zdarma, sloupec ukazuje zájem, ze kterého přicházejí trenéři. Bez práce týmu (výpočet po konzultaci s Honzou).</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/vystupy/nakladova-struktura.xlsx
+++ b/docs/vystupy/nakladova-struktura.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unit_Economics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CAPEX" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cashflow_12M" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit_Economics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cashflow_12M" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1544,7 +1544,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Příjmy = (aktivní klienti − 3 zdarma × platící trenéři) × 49 Kč, nejvýš strop 1 490 Kč na trenéra. Psovodi bez trenéra jsou zdarma, sloupec ukazuje zájem, ze kterého přicházejí trenéři. Bez práce týmu (výpočet po konzultaci s Honzou).</t>
+          <t>Příjmy = (aktivní klienti − 3 zdarma × platící trenéři) × 49 Kč, nejvýš strop 1 490 Kč na trenéra. Psovodi bez trenéra jsou zdarma, sloupec ukazuje zájem, ze kterého přicházejí trenéři. Bez práce týmu (výpočet po konzultaci s Honzou). E-maily (pozvánky, obnova hesla, F-48) do M07 v bezplatném tarifu e-mailové služby, od M08 placený tarif ve sloupci Notifikace.</t>
         </is>
       </c>
     </row>
